--- a/Australia_Crime_Statistics.xlsx
+++ b/Australia_Crime_Statistics.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oscar\source\repos\Neural Network Application\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oscar\source\repos\Australia Crime Statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810038E7-535F-4670-83AC-5DF69DBB8184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -6180,7 +6180,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="E2">
-        <f>D2</f>
+        <f t="shared" ref="E2:E10" si="0">D2</f>
         <v>0.33700000000000002</v>
       </c>
     </row>
@@ -6192,11 +6192,11 @@
         <v>0.25</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D10" si="0">C3+B3</f>
+        <f t="shared" ref="D3:D10" si="1">C3+B3</f>
         <v>0.25</v>
       </c>
       <c r="E3">
-        <f>D3</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
@@ -6208,11 +6208,11 @@
         <v>0.317</v>
       </c>
       <c r="D4">
+        <f t="shared" si="1"/>
+        <v>0.317</v>
+      </c>
+      <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.317</v>
-      </c>
-      <c r="E4">
-        <f>D4</f>
         <v>0.317</v>
       </c>
     </row>
@@ -6224,11 +6224,11 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="D5">
+        <f t="shared" si="1"/>
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="E5">
-        <f>D5</f>
         <v>0.41599999999999998</v>
       </c>
     </row>
@@ -6240,11 +6240,11 @@
         <v>0.373</v>
       </c>
       <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0.373</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="0"/>
-        <v>0.373</v>
-      </c>
-      <c r="E6">
-        <f>D6</f>
         <v>0.373</v>
       </c>
     </row>
@@ -6256,11 +6256,11 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="D7">
+        <f t="shared" si="1"/>
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="E7">
-        <f>D7</f>
         <v>0.40400000000000003</v>
       </c>
     </row>
@@ -6272,11 +6272,11 @@
         <v>0.33</v>
       </c>
       <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0.33</v>
+      </c>
+      <c r="E8">
         <f t="shared" si="0"/>
-        <v>0.33</v>
-      </c>
-      <c r="E8">
-        <f>D8</f>
         <v>0.33</v>
       </c>
     </row>
@@ -6288,11 +6288,11 @@
         <v>0.35299999999999998</v>
       </c>
       <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="0"/>
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="E9">
-        <f>D9</f>
         <v>0.35299999999999998</v>
       </c>
     </row>
@@ -6304,11 +6304,11 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="D10">
+        <f t="shared" si="1"/>
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="E10">
         <f t="shared" si="0"/>
-        <v>0.21199999999999999</v>
-      </c>
-      <c r="E10">
-        <f>D10</f>
         <v>0.21199999999999999</v>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
         <v>0.38</v>
       </c>
       <c r="D17">
-        <f t="shared" ref="D17:D26" si="1">SUM(B17:C17)</f>
+        <f t="shared" ref="D17:D26" si="2">SUM(B17:C17)</f>
         <v>0.38</v>
       </c>
       <c r="E17">
@@ -6378,7 +6378,7 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="D18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.30599999999999999</v>
       </c>
       <c r="E18">
@@ -6394,7 +6394,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="D19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.33700000000000002</v>
       </c>
       <c r="E19">
@@ -6410,7 +6410,7 @@
         <v>0.50800000000000001</v>
       </c>
       <c r="D20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.50800000000000001</v>
       </c>
       <c r="E20">
@@ -6426,7 +6426,7 @@
         <v>0.19900000000000001</v>
       </c>
       <c r="D21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.19900000000000001</v>
       </c>
       <c r="E21">
@@ -6490,7 +6490,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="D25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.44400000000000001</v>
       </c>
       <c r="E25">
@@ -6506,7 +6506,7 @@
         <v>0.318</v>
       </c>
       <c r="D26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.318</v>
       </c>
       <c r="E26">
@@ -6522,7 +6522,7 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="D27">
-        <f t="shared" ref="D27:D39" si="2">SUM(B27:C27)</f>
+        <f t="shared" ref="D27:D39" si="3">SUM(B27:C27)</f>
         <v>0.44900000000000001</v>
       </c>
       <c r="E27">
@@ -6538,7 +6538,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="D28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.21199999999999999</v>
       </c>
       <c r="E28">
@@ -6554,7 +6554,7 @@
         <v>0.219</v>
       </c>
       <c r="D29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.219</v>
       </c>
       <c r="E29">
@@ -6570,7 +6570,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="D30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.33500000000000002</v>
       </c>
       <c r="E30">
@@ -6586,7 +6586,7 @@
         <v>0.159</v>
       </c>
       <c r="D31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.159</v>
       </c>
       <c r="E31">
@@ -6602,7 +6602,7 @@
         <v>0.20200000000000001</v>
       </c>
       <c r="D32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.20200000000000001</v>
       </c>
       <c r="E32">
@@ -6618,7 +6618,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="D33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14199999999999999</v>
       </c>
       <c r="E33">
@@ -6634,7 +6634,7 @@
         <v>0.24</v>
       </c>
       <c r="D34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.24</v>
       </c>
       <c r="E34">
@@ -6650,7 +6650,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="D35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.27700000000000002</v>
       </c>
       <c r="E35">
@@ -6666,7 +6666,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="D36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.29699999999999999</v>
       </c>
       <c r="E36">
@@ -6682,7 +6682,7 @@
         <v>0.3</v>
       </c>
       <c r="D37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="E37">
@@ -6698,7 +6698,7 @@
         <v>0.33600000000000002</v>
       </c>
       <c r="D38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.33600000000000002</v>
       </c>
       <c r="E38">
@@ -6714,7 +6714,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="D39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.44600000000000001</v>
       </c>
       <c r="E39">
@@ -6730,7 +6730,7 @@
         <v>0.46899999999999997</v>
       </c>
       <c r="D40">
-        <f t="shared" ref="D40:D87" si="3">SUM(B40:C40)</f>
+        <f t="shared" ref="D40:D87" si="4">SUM(B40:C40)</f>
         <v>0.46899999999999997</v>
       </c>
       <c r="E40">
@@ -6746,7 +6746,7 @@
         <v>0.46700000000000003</v>
       </c>
       <c r="D41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.46700000000000003</v>
       </c>
       <c r="E41">
@@ -6762,7 +6762,7 @@
         <v>0.4</v>
       </c>
       <c r="D42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="E42">
@@ -6778,7 +6778,7 @@
         <v>0.33200000000000002</v>
       </c>
       <c r="D43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.33200000000000002</v>
       </c>
       <c r="E43">
@@ -6794,7 +6794,7 @@
         <v>0.39</v>
       </c>
       <c r="D44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.39</v>
       </c>
       <c r="E44">
@@ -6810,7 +6810,7 @@
         <v>0.435</v>
       </c>
       <c r="D45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.435</v>
       </c>
       <c r="E45">
@@ -6826,7 +6826,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="D46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.33400000000000002</v>
       </c>
       <c r="E46">
@@ -6842,7 +6842,7 @@
         <v>0.39600000000000002</v>
       </c>
       <c r="D47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.39600000000000002</v>
       </c>
       <c r="E47">
@@ -6858,7 +6858,7 @@
         <v>0.183</v>
       </c>
       <c r="D48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.183</v>
       </c>
       <c r="E48">
@@ -6874,7 +6874,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="D49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.14499999999999999</v>
       </c>
       <c r="E49">
@@ -6890,7 +6890,7 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="D50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.41599999999999998</v>
       </c>
       <c r="E50">
@@ -6906,7 +6906,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="D51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.27400000000000002</v>
       </c>
       <c r="E51">
@@ -6922,7 +6922,7 @@
         <v>0.36699999999999999</v>
       </c>
       <c r="D52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.36699999999999999</v>
       </c>
       <c r="E52">
@@ -6938,7 +6938,7 @@
         <v>0.246</v>
       </c>
       <c r="D53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.246</v>
       </c>
       <c r="E53">
@@ -6954,7 +6954,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="D54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.40100000000000002</v>
       </c>
       <c r="E54">
@@ -6970,7 +6970,7 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="D55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.28599999999999998</v>
       </c>
       <c r="E55">
@@ -6986,7 +6986,7 @@
         <v>0.33200000000000002</v>
       </c>
       <c r="D56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.33200000000000002</v>
       </c>
       <c r="E56">
@@ -7002,7 +7002,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="D57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="E57">
@@ -7018,7 +7018,7 @@
         <v>0.32600000000000001</v>
       </c>
       <c r="D58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.32600000000000001</v>
       </c>
       <c r="E58">
@@ -7034,7 +7034,7 @@
         <v>0.374</v>
       </c>
       <c r="D59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.374</v>
       </c>
       <c r="E59">
@@ -7050,7 +7050,7 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="D60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.45400000000000001</v>
       </c>
       <c r="E60">
@@ -7066,7 +7066,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="D61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.25600000000000001</v>
       </c>
       <c r="E61">
@@ -7082,7 +7082,7 @@
         <v>0.48</v>
       </c>
       <c r="D62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.48</v>
       </c>
       <c r="E62">
@@ -7098,7 +7098,7 @@
         <v>0.47</v>
       </c>
       <c r="D63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47</v>
       </c>
       <c r="E63">
@@ -7114,7 +7114,7 @@
         <v>0.39600000000000002</v>
       </c>
       <c r="D64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.39600000000000002</v>
       </c>
       <c r="E64">
@@ -7130,7 +7130,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="D65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29799999999999999</v>
       </c>
       <c r="E65">
@@ -7146,7 +7146,7 @@
         <v>0.33</v>
       </c>
       <c r="D66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.33</v>
       </c>
       <c r="E66">
@@ -7162,7 +7162,7 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="D67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.34300000000000003</v>
       </c>
       <c r="E67">
@@ -7178,7 +7178,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="D68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.14199999999999999</v>
       </c>
       <c r="E68">
@@ -7194,7 +7194,7 @@
         <v>0.219</v>
       </c>
       <c r="D69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.219</v>
       </c>
       <c r="E69">
@@ -7210,7 +7210,7 @@
         <v>0.317</v>
       </c>
       <c r="D70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.317</v>
       </c>
       <c r="E70">
@@ -7226,7 +7226,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="D71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.22500000000000001</v>
       </c>
       <c r="E71">
@@ -7242,7 +7242,7 @@
         <v>0.34699999999999998</v>
       </c>
       <c r="D72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.34699999999999998</v>
       </c>
       <c r="E72">
@@ -7258,7 +7258,7 @@
         <v>0.375</v>
       </c>
       <c r="D73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.375</v>
       </c>
       <c r="E73">
@@ -7274,7 +7274,7 @@
         <v>0.3</v>
       </c>
       <c r="D74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="E74">
@@ -7290,7 +7290,7 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="D75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.28499999999999998</v>
       </c>
       <c r="E75">
@@ -7306,7 +7306,7 @@
         <v>0.45</v>
       </c>
       <c r="D76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="E76">
@@ -7322,7 +7322,7 @@
         <v>0.24299999999999999</v>
       </c>
       <c r="D77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.24299999999999999</v>
       </c>
       <c r="E77">
@@ -7338,7 +7338,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="E78">
@@ -7354,7 +7354,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="D79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.28399999999999997</v>
       </c>
       <c r="E79">
@@ -7370,7 +7370,7 @@
         <v>0.247</v>
       </c>
       <c r="D80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.247</v>
       </c>
       <c r="E80">
@@ -7386,7 +7386,7 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="D81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29099999999999998</v>
       </c>
       <c r="E81">
@@ -7402,7 +7402,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.16600000000000001</v>
       </c>
       <c r="E82">
@@ -7418,7 +7418,7 @@
         <v>0.217</v>
       </c>
       <c r="D83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.217</v>
       </c>
       <c r="E83">
@@ -7434,7 +7434,7 @@
         <v>0.2</v>
       </c>
       <c r="D84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="E84">
@@ -7450,7 +7450,7 @@
         <v>0.11</v>
       </c>
       <c r="D85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.11</v>
       </c>
       <c r="E85">
@@ -7466,7 +7466,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="D86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.25900000000000001</v>
       </c>
       <c r="E86">
@@ -7482,7 +7482,7 @@
         <v>0.191</v>
       </c>
       <c r="D87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.191</v>
       </c>
       <c r="E87">
